--- a/data/nzd0172/nzd0172.xlsx
+++ b/data/nzd0172/nzd0172.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G404"/>
+  <dimension ref="A1:G405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11322,6 +11322,33 @@
       <c r="G404" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>387.87</v>
+      </c>
+      <c r="C405" t="n">
+        <v>387.55</v>
+      </c>
+      <c r="D405" t="n">
+        <v>384.96</v>
+      </c>
+      <c r="E405" t="n">
+        <v>382.65</v>
+      </c>
+      <c r="F405" t="n">
+        <v>381.83</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B453"/>
+  <dimension ref="A1:B454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15869,6 +15896,16 @@
       </c>
       <c r="B453" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -16037,28 +16074,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3622148259568516</v>
+        <v>0.3602006744458232</v>
       </c>
       <c r="J2" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K2" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2815632739429849</v>
+        <v>0.279862259138251</v>
       </c>
       <c r="M2" t="n">
-        <v>3.446583273763382</v>
+        <v>3.447609864042345</v>
       </c>
       <c r="N2" t="n">
-        <v>19.06981905533554</v>
+        <v>19.06668762047855</v>
       </c>
       <c r="O2" t="n">
-        <v>4.366900394482973</v>
+        <v>4.36654183771077</v>
       </c>
       <c r="P2" t="n">
-        <v>382.5524902948328</v>
+        <v>382.5733133374417</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -16119,28 +16156,28 @@
         <v>0.0755</v>
       </c>
       <c r="I3" t="n">
-        <v>0.183273343523305</v>
+        <v>0.1849148083563279</v>
       </c>
       <c r="J3" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K3" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1879156230538935</v>
+        <v>0.1908460964959056</v>
       </c>
       <c r="M3" t="n">
-        <v>2.259405678417078</v>
+        <v>2.263039059747133</v>
       </c>
       <c r="N3" t="n">
-        <v>8.419414543119393</v>
+        <v>8.429934930961817</v>
       </c>
       <c r="O3" t="n">
-        <v>2.901622743073157</v>
+        <v>2.903435022686373</v>
       </c>
       <c r="P3" t="n">
-        <v>379.1450616020068</v>
+        <v>379.1283343842579</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16201,28 +16238,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1657269416805708</v>
+        <v>0.1639235884302433</v>
       </c>
       <c r="J4" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K4" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1460772161061746</v>
+        <v>0.1434814084730257</v>
       </c>
       <c r="M4" t="n">
-        <v>2.269625804089499</v>
+        <v>2.274676653893572</v>
       </c>
       <c r="N4" t="n">
-        <v>9.312523244373095</v>
+        <v>9.32732382646571</v>
       </c>
       <c r="O4" t="n">
-        <v>3.051642712437531</v>
+        <v>3.054066768501584</v>
       </c>
       <c r="P4" t="n">
-        <v>384.5183649194758</v>
+        <v>384.5367418483563</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -16283,28 +16320,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1455990310819554</v>
+        <v>0.1432861690811136</v>
       </c>
       <c r="J5" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K5" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1043189954090317</v>
+        <v>0.101281374892309</v>
       </c>
       <c r="M5" t="n">
-        <v>2.358700516660422</v>
+        <v>2.365065259257587</v>
       </c>
       <c r="N5" t="n">
-        <v>10.55727799627507</v>
+        <v>10.59340761884164</v>
       </c>
       <c r="O5" t="n">
-        <v>3.249196515490418</v>
+        <v>3.254751544871227</v>
       </c>
       <c r="P5" t="n">
-        <v>383.8463168433032</v>
+        <v>383.8698858808681</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -16365,28 +16402,28 @@
         <v>0.1629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05360527052057699</v>
+        <v>0.05151009325166978</v>
       </c>
       <c r="J6" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K6" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01979604613072117</v>
+        <v>0.0182862610004626</v>
       </c>
       <c r="M6" t="n">
-        <v>2.186297899079165</v>
+        <v>2.193593620945217</v>
       </c>
       <c r="N6" t="n">
-        <v>8.123355376034016</v>
+        <v>8.153117349512561</v>
       </c>
       <c r="O6" t="n">
-        <v>2.850150062020247</v>
+        <v>2.855366412478889</v>
       </c>
       <c r="P6" t="n">
-        <v>384.9126564296254</v>
+        <v>384.9342654710355</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -16428,7 +16465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G404"/>
+  <dimension ref="A1:G405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31331,6 +31368,43 @@
         </is>
       </c>
     </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>-36.78569131773114,175.09787406260378</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>-36.78557427704735,175.09870395110607</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>-36.785405366518994,175.0995483057347</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>-36.785175011814225,175.10038295987263</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>-36.78491078547658,175.10121512775154</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0172/nzd0172.xlsx
+++ b/data/nzd0172/nzd0172.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G405"/>
+  <dimension ref="A1:G406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11349,6 +11349,33 @@
       <c r="G405" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>386.55</v>
+      </c>
+      <c r="C406" t="n">
+        <v>388.71</v>
+      </c>
+      <c r="D406" t="n">
+        <v>385.7</v>
+      </c>
+      <c r="E406" t="n">
+        <v>382.75</v>
+      </c>
+      <c r="F406" t="n">
+        <v>380.14</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11363,7 +11390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B454"/>
+  <dimension ref="A1:B455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15906,6 +15933,16 @@
       </c>
       <c r="B454" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>
@@ -16074,28 +16111,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3602006744458232</v>
+        <v>0.3575895112808964</v>
       </c>
       <c r="J2" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K2" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L2" t="n">
-        <v>0.279862259138251</v>
+        <v>0.2771487403060651</v>
       </c>
       <c r="M2" t="n">
-        <v>3.447609864042345</v>
+        <v>3.451492358594269</v>
       </c>
       <c r="N2" t="n">
-        <v>19.06668762047855</v>
+        <v>19.09515939217394</v>
       </c>
       <c r="O2" t="n">
-        <v>4.36654183771077</v>
+        <v>4.369800841248254</v>
       </c>
       <c r="P2" t="n">
-        <v>382.5733133374417</v>
+        <v>382.6003370286306</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -16156,28 +16193,28 @@
         <v>0.0755</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1849148083563279</v>
+        <v>0.1870618658673344</v>
       </c>
       <c r="J3" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K3" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1908460964959056</v>
+        <v>0.1942085071431645</v>
       </c>
       <c r="M3" t="n">
-        <v>2.263039059747133</v>
+        <v>2.269561488968579</v>
       </c>
       <c r="N3" t="n">
-        <v>8.429934930961817</v>
+        <v>8.463225455511163</v>
       </c>
       <c r="O3" t="n">
-        <v>2.903435022686373</v>
+        <v>2.909162328834739</v>
       </c>
       <c r="P3" t="n">
-        <v>379.1283343842579</v>
+        <v>379.1064315376461</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16238,28 +16275,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1639235884302433</v>
+        <v>0.1624785476100697</v>
       </c>
       <c r="J4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K4" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1434814084730257</v>
+        <v>0.1416010112164396</v>
       </c>
       <c r="M4" t="n">
-        <v>2.274676653893572</v>
+        <v>2.277586045217218</v>
       </c>
       <c r="N4" t="n">
-        <v>9.32732382646571</v>
+        <v>9.328801613950302</v>
       </c>
       <c r="O4" t="n">
-        <v>3.054066768501584</v>
+        <v>3.054308696571174</v>
       </c>
       <c r="P4" t="n">
-        <v>384.5367418483563</v>
+        <v>384.5514831895965</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -16320,28 +16357,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1432861690811136</v>
+        <v>0.1410462939278162</v>
       </c>
       <c r="J5" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K5" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L5" t="n">
-        <v>0.101281374892309</v>
+        <v>0.0983954610414699</v>
       </c>
       <c r="M5" t="n">
-        <v>2.365065259257587</v>
+        <v>2.370989205240894</v>
       </c>
       <c r="N5" t="n">
-        <v>10.59340761884164</v>
+        <v>10.62613530100484</v>
       </c>
       <c r="O5" t="n">
-        <v>3.254751544871227</v>
+        <v>3.259775345174087</v>
       </c>
       <c r="P5" t="n">
-        <v>383.8698858808681</v>
+        <v>383.8927355910695</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -16402,28 +16439,28 @@
         <v>0.1629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05151009325166978</v>
+        <v>0.0486616006304247</v>
       </c>
       <c r="J6" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K6" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0182862610004626</v>
+        <v>0.01624924637216718</v>
       </c>
       <c r="M6" t="n">
-        <v>2.193593620945217</v>
+        <v>2.205394921261248</v>
       </c>
       <c r="N6" t="n">
-        <v>8.153117349512561</v>
+        <v>8.226027960134751</v>
       </c>
       <c r="O6" t="n">
-        <v>2.855366412478889</v>
+        <v>2.868105290977783</v>
       </c>
       <c r="P6" t="n">
-        <v>384.9342654710355</v>
+        <v>384.9636750196778</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -16465,7 +16502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G405"/>
+  <dimension ref="A1:G406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31405,6 +31442,43 @@
         </is>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>-36.78570298750678,175.09787692253164</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>-36.785564138325924,175.0987007904292</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>-36.78539907088219,175.0995455740858</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>-36.78517417835876,175.10038253406057</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>-36.78492479479151,175.10122254994133</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0172/nzd0172.xlsx
+++ b/data/nzd0172/nzd0172.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G406"/>
+  <dimension ref="A1:G408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11374,6 +11374,60 @@
         <v>380.14</v>
       </c>
       <c r="G406" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>387.06</v>
+      </c>
+      <c r="C407" t="n">
+        <v>381.82</v>
+      </c>
+      <c r="D407" t="n">
+        <v>382.39</v>
+      </c>
+      <c r="E407" t="n">
+        <v>382.55</v>
+      </c>
+      <c r="F407" t="n">
+        <v>383.19</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>387.06</v>
+      </c>
+      <c r="C408" t="n">
+        <v>382.61</v>
+      </c>
+      <c r="D408" t="n">
+        <v>385.95</v>
+      </c>
+      <c r="E408" t="n">
+        <v>387</v>
+      </c>
+      <c r="F408" t="n">
+        <v>387.05</v>
+      </c>
+      <c r="G408" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11390,7 +11444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B455"/>
+  <dimension ref="A1:B457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15943,6 +15997,26 @@
       </c>
       <c r="B455" t="n">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -16111,28 +16185,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3575895112808964</v>
+        <v>0.3528975038815794</v>
       </c>
       <c r="J2" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K2" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2771487403060651</v>
+        <v>0.2726044323791372</v>
       </c>
       <c r="M2" t="n">
-        <v>3.451492358594269</v>
+        <v>3.457214787312569</v>
       </c>
       <c r="N2" t="n">
-        <v>19.09515939217394</v>
+        <v>19.12328460432344</v>
       </c>
       <c r="O2" t="n">
-        <v>4.369800841248254</v>
+        <v>4.373017791448308</v>
       </c>
       <c r="P2" t="n">
-        <v>382.6003370286306</v>
+        <v>382.6490750970798</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -16193,28 +16267,28 @@
         <v>0.0755</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1870618658673344</v>
+        <v>0.1853937855033298</v>
       </c>
       <c r="J3" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K3" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1942085071431645</v>
+        <v>0.1926410862500508</v>
       </c>
       <c r="M3" t="n">
-        <v>2.269561488968579</v>
+        <v>2.266902117636404</v>
       </c>
       <c r="N3" t="n">
-        <v>8.463225455511163</v>
+        <v>8.438787152514818</v>
       </c>
       <c r="O3" t="n">
-        <v>2.909162328834739</v>
+        <v>2.904959062106525</v>
       </c>
       <c r="P3" t="n">
-        <v>379.1064315376461</v>
+        <v>379.1235098134944</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16275,28 +16349,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1624785476100697</v>
+        <v>0.1582344261362957</v>
       </c>
       <c r="J4" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K4" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1416010112164396</v>
+        <v>0.1349243468545164</v>
       </c>
       <c r="M4" t="n">
-        <v>2.277586045217218</v>
+        <v>2.291237751840893</v>
       </c>
       <c r="N4" t="n">
-        <v>9.328801613950302</v>
+        <v>9.404542643210263</v>
       </c>
       <c r="O4" t="n">
-        <v>3.054308696571174</v>
+        <v>3.066682677293212</v>
       </c>
       <c r="P4" t="n">
-        <v>384.5514831895965</v>
+        <v>384.594931857691</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -16357,28 +16431,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1410462939278162</v>
+        <v>0.1384621665528313</v>
       </c>
       <c r="J5" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K5" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0983954610414699</v>
+        <v>0.09549975548737233</v>
       </c>
       <c r="M5" t="n">
-        <v>2.370989205240894</v>
+        <v>2.37291374143298</v>
       </c>
       <c r="N5" t="n">
-        <v>10.62613530100484</v>
+        <v>10.63752606035086</v>
       </c>
       <c r="O5" t="n">
-        <v>3.259775345174087</v>
+        <v>3.261522046583597</v>
       </c>
       <c r="P5" t="n">
-        <v>383.8927355910695</v>
+        <v>383.9191845971284</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -16439,28 +16513,28 @@
         <v>0.1629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0486616006304247</v>
+        <v>0.04762310845898663</v>
       </c>
       <c r="J6" t="n">
+        <v>407</v>
+      </c>
+      <c r="K6" t="n">
         <v>405</v>
       </c>
-      <c r="K6" t="n">
-        <v>403</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01624924637216718</v>
+        <v>0.01568097285336423</v>
       </c>
       <c r="M6" t="n">
-        <v>2.205394921261248</v>
+        <v>2.204813572130815</v>
       </c>
       <c r="N6" t="n">
-        <v>8.226027960134751</v>
+        <v>8.209979207642091</v>
       </c>
       <c r="O6" t="n">
-        <v>2.868105290977783</v>
+        <v>2.865306128085111</v>
       </c>
       <c r="P6" t="n">
-        <v>384.9636750196778</v>
+        <v>384.9744268602166</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -16502,7 +16576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G406"/>
+  <dimension ref="A1:G408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31479,6 +31553,80 @@
         </is>
       </c>
     </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>-36.78569847872984,175.0978758175594</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>-36.78562435883328,175.09871956377316</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>-36.785427231094786,175.09955779268108</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>-36.78517584526968,175.10038338568472</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>-36.78489951170794,175.10120915486715</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>-36.78569847872984,175.0978758175594</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>-36.785617454014826,175.09871741124007</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>-36.78539694397785,175.09954465123155</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>-36.78513875649959,175.10036443705678</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>-36.78486751409784,175.10119220242575</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0172/nzd0172.xlsx
+++ b/data/nzd0172/nzd0172.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G408"/>
+  <dimension ref="A1:G409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11428,6 +11428,33 @@
         <v>387.05</v>
       </c>
       <c r="G408" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>384.81</v>
+      </c>
+      <c r="C409" t="n">
+        <v>381.97</v>
+      </c>
+      <c r="D409" t="n">
+        <v>385.37</v>
+      </c>
+      <c r="E409" t="n">
+        <v>386.12</v>
+      </c>
+      <c r="F409" t="n">
+        <v>386.99</v>
+      </c>
+      <c r="G409" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11444,7 +11471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B457"/>
+  <dimension ref="A1:B458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16017,6 +16044,16 @@
       </c>
       <c r="B457" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
@@ -16185,34 +16222,30 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3528975038815794</v>
+        <v>0.349509580584737</v>
       </c>
       <c r="J2" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K2" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2726044323791372</v>
+        <v>0.2684613968886888</v>
       </c>
       <c r="M2" t="n">
-        <v>3.457214787312569</v>
+        <v>3.465761100795419</v>
       </c>
       <c r="N2" t="n">
-        <v>19.12328460432344</v>
+        <v>19.20512636997049</v>
       </c>
       <c r="O2" t="n">
-        <v>4.373017791448308</v>
+        <v>4.382365385265187</v>
       </c>
       <c r="P2" t="n">
-        <v>382.6490750970798</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>382.6844330977422</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (175.09871446733484 -36.789120370150826, 175.09672259898304 -36.78099250981126)</t>
@@ -16267,34 +16300,30 @@
         <v>0.0755</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1853937855033298</v>
+        <v>0.1844474734355588</v>
       </c>
       <c r="J3" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K3" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1926410862500508</v>
+        <v>0.191628897590807</v>
       </c>
       <c r="M3" t="n">
-        <v>2.266902117636404</v>
+        <v>2.266159715200261</v>
       </c>
       <c r="N3" t="n">
-        <v>8.438787152514818</v>
+        <v>8.428664976797398</v>
       </c>
       <c r="O3" t="n">
-        <v>2.904959062106525</v>
+        <v>2.903216315880957</v>
       </c>
       <c r="P3" t="n">
-        <v>379.1235098134944</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>379.1332458586495</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (175.09975996699887 -36.78896156434974, 175.0972549196301 -36.78092580448161)</t>
@@ -16349,34 +16378,30 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1582344261362957</v>
+        <v>0.1566775492017261</v>
       </c>
       <c r="J4" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K4" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1349243468545164</v>
+        <v>0.1328543964415209</v>
       </c>
       <c r="M4" t="n">
-        <v>2.291237751840893</v>
+        <v>2.294839438325929</v>
       </c>
       <c r="N4" t="n">
-        <v>9.404542643210263</v>
+        <v>9.410078073229043</v>
       </c>
       <c r="O4" t="n">
-        <v>3.066682677293212</v>
+        <v>3.06758505558184</v>
       </c>
       <c r="P4" t="n">
-        <v>384.594931857691</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>384.610949643633</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (175.10096941743188 -36.788680447594004, 175.09757536184168 -36.78085801517893)</t>
@@ -16431,34 +16456,30 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1384621665528313</v>
+        <v>0.1377892331988306</v>
       </c>
       <c r="J5" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K5" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09549975548737233</v>
+        <v>0.09504469634265666</v>
       </c>
       <c r="M5" t="n">
-        <v>2.37291374143298</v>
+        <v>2.370628542865506</v>
       </c>
       <c r="N5" t="n">
-        <v>10.63752606035086</v>
+        <v>10.61679423759166</v>
       </c>
       <c r="O5" t="n">
-        <v>3.261522046583597</v>
+        <v>3.258342252985658</v>
       </c>
       <c r="P5" t="n">
-        <v>383.9191845971284</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>383.9261080103914</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (175.10201240002604 -36.788364215046116, 175.09809708029596 -36.780700488723305)</t>
@@ -16513,34 +16534,30 @@
         <v>0.1629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04762310845898663</v>
+        <v>0.04796911341883537</v>
       </c>
       <c r="J6" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K6" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01568097285336423</v>
+        <v>0.01598182327567099</v>
       </c>
       <c r="M6" t="n">
-        <v>2.204813572130815</v>
+        <v>2.200957520058654</v>
       </c>
       <c r="N6" t="n">
-        <v>8.209979207642091</v>
+        <v>8.191138500645767</v>
       </c>
       <c r="O6" t="n">
-        <v>2.865306128085111</v>
+        <v>2.862016509499162</v>
       </c>
       <c r="P6" t="n">
-        <v>384.9744268602166</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>384.9708244134856</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (175.10289213086608 -36.788075964057796, 175.09885380847493 -36.780453518653665)</t>
@@ -16576,7 +16593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G408"/>
+  <dimension ref="A1:G409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31627,6 +31644,43 @@
         </is>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>-36.78571837039268,175.09788069243797</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>-36.78562304779181,175.09871915506432</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>-36.785401878395916,175.09954679225348</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-36.785146090908356,175.10036818419965</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>-36.784868011470046,175.10119246593507</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0172/nzd0172.xlsx
+++ b/data/nzd0172/nzd0172.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G409"/>
+  <dimension ref="A1:G411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11457,6 +11457,60 @@
       <c r="G409" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>384.08</v>
+      </c>
+      <c r="C410" t="n">
+        <v>382.98</v>
+      </c>
+      <c r="D410" t="n">
+        <v>386.67</v>
+      </c>
+      <c r="E410" t="n">
+        <v>387.52</v>
+      </c>
+      <c r="F410" t="n">
+        <v>387.83</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>384.08</v>
+      </c>
+      <c r="C411" t="n">
+        <v>382.82</v>
+      </c>
+      <c r="D411" t="n">
+        <v>386.64</v>
+      </c>
+      <c r="E411" t="n">
+        <v>386.74</v>
+      </c>
+      <c r="F411" t="n">
+        <v>387.95</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B458"/>
+  <dimension ref="A1:B460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16054,6 +16108,26 @@
       </c>
       <c r="B458" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>
@@ -16222,28 +16296,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.349509580584737</v>
+        <v>0.3421390558633065</v>
       </c>
       <c r="J2" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K2" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2684613968886888</v>
+        <v>0.2590477763250757</v>
       </c>
       <c r="M2" t="n">
-        <v>3.465761100795419</v>
+        <v>3.485728124422844</v>
       </c>
       <c r="N2" t="n">
-        <v>19.20512636997049</v>
+        <v>19.41758411396044</v>
       </c>
       <c r="O2" t="n">
-        <v>4.382365385265187</v>
+        <v>4.406538790701886</v>
       </c>
       <c r="P2" t="n">
-        <v>382.6844330977422</v>
+        <v>382.7616342119455</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16300,28 +16374,28 @@
         <v>0.0755</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1844474734355588</v>
+        <v>0.1834122438424679</v>
       </c>
       <c r="J3" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K3" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L3" t="n">
-        <v>0.191628897590807</v>
+        <v>0.1913055378810927</v>
       </c>
       <c r="M3" t="n">
-        <v>2.266159715200261</v>
+        <v>2.260306069242175</v>
       </c>
       <c r="N3" t="n">
-        <v>8.428664976797398</v>
+        <v>8.393923670238635</v>
       </c>
       <c r="O3" t="n">
-        <v>2.903216315880957</v>
+        <v>2.897226893123601</v>
       </c>
       <c r="P3" t="n">
-        <v>379.1332458586495</v>
+        <v>379.1439370698944</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16378,28 +16452,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1566775492017261</v>
+        <v>0.1547537941995173</v>
       </c>
       <c r="J4" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K4" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1328543964415209</v>
+        <v>0.1308948438789699</v>
       </c>
       <c r="M4" t="n">
-        <v>2.294839438325929</v>
+        <v>2.295096288992569</v>
       </c>
       <c r="N4" t="n">
-        <v>9.410078073229043</v>
+        <v>9.38607108612965</v>
       </c>
       <c r="O4" t="n">
-        <v>3.06758505558184</v>
+        <v>3.06366954584362</v>
       </c>
       <c r="P4" t="n">
-        <v>384.610949643633</v>
+        <v>384.6308149178105</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16456,28 +16530,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1377892331988306</v>
+        <v>0.1373638418580359</v>
       </c>
       <c r="J5" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K5" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09504469634265666</v>
+        <v>0.09535226841383126</v>
       </c>
       <c r="M5" t="n">
-        <v>2.370628542865506</v>
+        <v>2.36126306946551</v>
       </c>
       <c r="N5" t="n">
-        <v>10.61679423759166</v>
+        <v>10.56683114641696</v>
       </c>
       <c r="O5" t="n">
-        <v>3.258342252985658</v>
+        <v>3.250666261924924</v>
       </c>
       <c r="P5" t="n">
-        <v>383.9261080103914</v>
+        <v>383.9305064704033</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16534,28 +16608,28 @@
         <v>0.1629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04796911341883537</v>
+        <v>0.04946733951549107</v>
       </c>
       <c r="J6" t="n">
+        <v>410</v>
+      </c>
+      <c r="K6" t="n">
         <v>408</v>
       </c>
-      <c r="K6" t="n">
-        <v>406</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01598182327567099</v>
+        <v>0.01711926641661876</v>
       </c>
       <c r="M6" t="n">
-        <v>2.200957520058654</v>
+        <v>2.196948027971975</v>
       </c>
       <c r="N6" t="n">
-        <v>8.191138500645767</v>
+        <v>8.163987929949238</v>
       </c>
       <c r="O6" t="n">
-        <v>2.862016509499162</v>
+        <v>2.857269313514083</v>
       </c>
       <c r="P6" t="n">
-        <v>384.9708244134856</v>
+        <v>384.9551682520715</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16593,7 +16667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G409"/>
+  <dimension ref="A1:G411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31681,6 +31755,80 @@
         </is>
       </c>
     </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>-36.7857248241321,175.09788227406582</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>-36.78561422011247,175.09871640309183</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>-36.78539081849329,175.0995419934116</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>-36.78513442253071,175.1003622228363</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>-36.784861048259174,175.10118877680463</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>-36.7857248241321,175.09788227406582</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>-36.785615618556726,175.09871683904785</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>-36.78539107372182,175.0995421041541</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-36.785140923484015,175.1003655441671</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>-36.78486005351475,175.10118824978605</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0172/nzd0172.xlsx
+++ b/data/nzd0172/nzd0172.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G411"/>
+  <dimension ref="A1:G413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11511,6 +11511,60 @@
       <c r="G411" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>386.91</v>
+      </c>
+      <c r="C412" t="n">
+        <v>382.17</v>
+      </c>
+      <c r="D412" t="n">
+        <v>386.46</v>
+      </c>
+      <c r="E412" t="n">
+        <v>386.46</v>
+      </c>
+      <c r="F412" t="n">
+        <v>387.57</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>387.08</v>
+      </c>
+      <c r="C413" t="n">
+        <v>382.61</v>
+      </c>
+      <c r="D413" t="n">
+        <v>387.18</v>
+      </c>
+      <c r="E413" t="n">
+        <v>387.39</v>
+      </c>
+      <c r="F413" t="n">
+        <v>388.28</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B460"/>
+  <dimension ref="A1:B462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16128,6 +16182,26 @@
       </c>
       <c r="B460" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>-0.72</v>
       </c>
     </row>
   </sheetData>
@@ -16296,28 +16370,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3421390558633065</v>
+        <v>0.3376022259740698</v>
       </c>
       <c r="J2" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K2" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2590477763250757</v>
+        <v>0.2547149636883986</v>
       </c>
       <c r="M2" t="n">
-        <v>3.485728124422844</v>
+        <v>3.491560481055544</v>
       </c>
       <c r="N2" t="n">
-        <v>19.41758411396044</v>
+        <v>19.43920730894469</v>
       </c>
       <c r="O2" t="n">
-        <v>4.406538790701886</v>
+        <v>4.40899164310216</v>
       </c>
       <c r="P2" t="n">
-        <v>382.7616342119455</v>
+        <v>382.8093250962003</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16374,28 +16448,28 @@
         <v>0.0755</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1834122438424679</v>
+        <v>0.1819320151526393</v>
       </c>
       <c r="J3" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K3" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1913055378810927</v>
+        <v>0.190081577225214</v>
       </c>
       <c r="M3" t="n">
-        <v>2.260306069242175</v>
+        <v>2.25668329071555</v>
       </c>
       <c r="N3" t="n">
-        <v>8.393923670238635</v>
+        <v>8.366519596886794</v>
       </c>
       <c r="O3" t="n">
-        <v>2.897226893123601</v>
+        <v>2.892493664104866</v>
       </c>
       <c r="P3" t="n">
-        <v>379.1439370698944</v>
+        <v>379.1592759183388</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16452,28 +16526,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1547537941995173</v>
+        <v>0.1530107864286169</v>
       </c>
       <c r="J4" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K4" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1308948438789699</v>
+        <v>0.1292212284924943</v>
       </c>
       <c r="M4" t="n">
-        <v>2.295096288992569</v>
+        <v>2.294253672336775</v>
       </c>
       <c r="N4" t="n">
-        <v>9.38607108612965</v>
+        <v>9.359300338088264</v>
       </c>
       <c r="O4" t="n">
-        <v>3.06366954584362</v>
+        <v>3.05929736019372</v>
       </c>
       <c r="P4" t="n">
-        <v>384.6308149178105</v>
+        <v>384.6488758703581</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16530,28 +16604,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1373638418580359</v>
+        <v>0.1367594540675172</v>
       </c>
       <c r="J5" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K5" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09535226841383126</v>
+        <v>0.09541659140513781</v>
       </c>
       <c r="M5" t="n">
-        <v>2.36126306946551</v>
+        <v>2.352898818050067</v>
       </c>
       <c r="N5" t="n">
-        <v>10.56683114641696</v>
+        <v>10.5187651451402</v>
       </c>
       <c r="O5" t="n">
-        <v>3.250666261924924</v>
+        <v>3.243264581427208</v>
       </c>
       <c r="P5" t="n">
-        <v>383.9305064704033</v>
+        <v>383.9367658016662</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16608,28 +16682,28 @@
         <v>0.1629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04946733951549107</v>
+        <v>0.05096528144940324</v>
       </c>
       <c r="J6" t="n">
+        <v>412</v>
+      </c>
+      <c r="K6" t="n">
         <v>410</v>
       </c>
-      <c r="K6" t="n">
-        <v>408</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01711926641661876</v>
+        <v>0.01830025226128662</v>
       </c>
       <c r="M6" t="n">
-        <v>2.196948027971975</v>
+        <v>2.192974414852836</v>
       </c>
       <c r="N6" t="n">
-        <v>8.163987929949238</v>
+        <v>8.137882908359503</v>
       </c>
       <c r="O6" t="n">
-        <v>2.857269313514083</v>
+        <v>2.8526974792921</v>
       </c>
       <c r="P6" t="n">
-        <v>384.9551682520715</v>
+        <v>384.9394559439487</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16667,7 +16741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G411"/>
+  <dimension ref="A1:G413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31829,6 +31903,80 @@
         </is>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>-36.78569980484072,175.0978761425512</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>-36.7856212997365,175.09871861011922</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>-36.785392605092966,175.09954276860904</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-36.78514325715954,175.10036673643984</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>-36.78486320353874,175.10118991867827</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>-36.785698301915055,175.09787577422716</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>-36.785617454014826,175.09871741124007</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>-36.78538647960835,175.09954011078943</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-36.78513550602295,175.10036277639142</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>-36.784857317967564,175.10118680048504</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0172/nzd0172.xlsx
+++ b/data/nzd0172/nzd0172.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G413"/>
+  <dimension ref="A1:G417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11565,6 +11565,114 @@
       <c r="G413" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>387.08</v>
+      </c>
+      <c r="C414" t="n">
+        <v>382.59</v>
+      </c>
+      <c r="D414" t="n">
+        <v>387.04</v>
+      </c>
+      <c r="E414" t="n">
+        <v>387.49</v>
+      </c>
+      <c r="F414" t="n">
+        <v>388.13</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>387.08</v>
+      </c>
+      <c r="C415" t="n">
+        <v>382.46</v>
+      </c>
+      <c r="D415" t="n">
+        <v>386.8</v>
+      </c>
+      <c r="E415" t="n">
+        <v>387.8</v>
+      </c>
+      <c r="F415" t="n">
+        <v>388.54</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>387.08</v>
+      </c>
+      <c r="C416" t="n">
+        <v>382.66</v>
+      </c>
+      <c r="D416" t="n">
+        <v>387.06</v>
+      </c>
+      <c r="E416" t="n">
+        <v>388.01</v>
+      </c>
+      <c r="F416" t="n">
+        <v>388.23</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>387.78</v>
+      </c>
+      <c r="C417" t="n">
+        <v>382.57</v>
+      </c>
+      <c r="D417" t="n">
+        <v>387.01</v>
+      </c>
+      <c r="E417" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="F417" t="n">
+        <v>388.54</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11579,7 +11687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B462"/>
+  <dimension ref="A1:B466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16202,6 +16310,46 @@
       </c>
       <c r="B462" t="n">
         <v>-0.72</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>-0.84</v>
       </c>
     </row>
   </sheetData>
@@ -16370,28 +16518,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3376022259740698</v>
+        <v>0.3292610241630894</v>
       </c>
       <c r="J2" t="n">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="K2" t="n">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2547149636883986</v>
+        <v>0.2470813779802166</v>
       </c>
       <c r="M2" t="n">
-        <v>3.491560481055544</v>
+        <v>3.49968243927808</v>
       </c>
       <c r="N2" t="n">
-        <v>19.43920730894469</v>
+        <v>19.45175513884131</v>
       </c>
       <c r="O2" t="n">
-        <v>4.40899164310216</v>
+        <v>4.410414395364829</v>
       </c>
       <c r="P2" t="n">
-        <v>382.8093250962003</v>
+        <v>382.8974091079835</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16448,28 +16596,28 @@
         <v>0.0755</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1819320151526393</v>
+        <v>0.1793534392532174</v>
       </c>
       <c r="J3" t="n">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="K3" t="n">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="L3" t="n">
-        <v>0.190081577225214</v>
+        <v>0.1883222084062641</v>
       </c>
       <c r="M3" t="n">
-        <v>2.25668329071555</v>
+        <v>2.247575436263133</v>
       </c>
       <c r="N3" t="n">
-        <v>8.366519596886794</v>
+        <v>8.306327397694588</v>
       </c>
       <c r="O3" t="n">
-        <v>2.892493664104866</v>
+        <v>2.882069984871046</v>
       </c>
       <c r="P3" t="n">
-        <v>379.1592759183388</v>
+        <v>379.186124937373</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16526,28 +16674,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1530107864286169</v>
+        <v>0.1499010152594541</v>
       </c>
       <c r="J4" t="n">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="K4" t="n">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1292212284924943</v>
+        <v>0.1264649196034459</v>
       </c>
       <c r="M4" t="n">
-        <v>2.294253672336775</v>
+        <v>2.290297731233217</v>
       </c>
       <c r="N4" t="n">
-        <v>9.359300338088264</v>
+        <v>9.298800467943725</v>
       </c>
       <c r="O4" t="n">
-        <v>3.05929736019372</v>
+        <v>3.04939345902488</v>
       </c>
       <c r="P4" t="n">
-        <v>384.6488758703581</v>
+        <v>384.6812558336074</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16604,28 +16752,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1367594540675172</v>
+        <v>0.1371894666024647</v>
       </c>
       <c r="J5" t="n">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="K5" t="n">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09541659140513781</v>
+        <v>0.09765784959832735</v>
       </c>
       <c r="M5" t="n">
-        <v>2.352898818050067</v>
+        <v>2.333235192665725</v>
       </c>
       <c r="N5" t="n">
-        <v>10.5187651451402</v>
+        <v>10.41869020713114</v>
       </c>
       <c r="O5" t="n">
-        <v>3.243264581427208</v>
+        <v>3.227799592157348</v>
       </c>
       <c r="P5" t="n">
-        <v>383.9367658016662</v>
+        <v>383.9322834973157</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16682,28 +16830,28 @@
         <v>0.1629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05096528144940324</v>
+        <v>0.05461344938732469</v>
       </c>
       <c r="J6" t="n">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="K6" t="n">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01830025226128662</v>
+        <v>0.02126107134359012</v>
       </c>
       <c r="M6" t="n">
-        <v>2.192974414852836</v>
+        <v>2.187925194093971</v>
       </c>
       <c r="N6" t="n">
-        <v>8.137882908359503</v>
+        <v>8.099131922449347</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8526974792921</v>
+        <v>2.845897384384994</v>
       </c>
       <c r="P6" t="n">
-        <v>384.9394559439487</v>
+        <v>384.9010189118291</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16741,7 +16889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G413"/>
+  <dimension ref="A1:G417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31977,6 +32125,154 @@
         </is>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>-36.785698301915055,175.09787577422716</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>-36.78561762882034,175.09871746573458</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>-36.78538767067481,175.0995406275877</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-36.785134672567374,175.1003623505798</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-36.78485856139811,175.10118745925823</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>-36.785698301915055,175.09787577422716</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>-36.78561876505629,175.09871781994886</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>-36.78538971250302,175.09954151352753</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-36.785132088855136,175.10036103056387</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>-36.78485516268795,175.10118565861157</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>-36.785698301915055,175.09787577422716</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>-36.78561701700099,175.09871727500382</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>-36.785387500522454,175.09954055375934</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-36.78513033859844,175.1003601363596</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-36.784857732444415,175.1011870200761</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>-36.78569211339765,175.09787425759885</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>-36.785617803625875,175.0987175202291</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-36.785387925903336,175.09954073833012</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-36.785129588488424,175.1003597531292</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-36.78485516268795,175.10118565861157</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0172/nzd0172.xlsx
+++ b/data/nzd0172/nzd0172.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G417"/>
+  <dimension ref="A1:G419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11671,6 +11671,60 @@
         <v>388.54</v>
       </c>
       <c r="G417" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>389.17</v>
+      </c>
+      <c r="C418" t="n">
+        <v>382.06</v>
+      </c>
+      <c r="D418" t="n">
+        <v>386.97</v>
+      </c>
+      <c r="E418" t="n">
+        <v>388.25</v>
+      </c>
+      <c r="F418" t="n">
+        <v>389.44</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>389.55</v>
+      </c>
+      <c r="C419" t="n">
+        <v>381.9</v>
+      </c>
+      <c r="D419" t="n">
+        <v>387.18</v>
+      </c>
+      <c r="E419" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="F419" t="n">
+        <v>389.67</v>
+      </c>
+      <c r="G419" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11687,7 +11741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16350,6 +16404,26 @@
       </c>
       <c r="B466" t="n">
         <v>-0.84</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>-0.89</v>
       </c>
     </row>
   </sheetData>
@@ -16518,28 +16592,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3292610241630894</v>
+        <v>0.3271027293608741</v>
       </c>
       <c r="J2" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K2" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2470813779802166</v>
+        <v>0.2462024530035677</v>
       </c>
       <c r="M2" t="n">
-        <v>3.49968243927808</v>
+        <v>3.493673711769219</v>
       </c>
       <c r="N2" t="n">
-        <v>19.45175513884131</v>
+        <v>19.3843763480776</v>
       </c>
       <c r="O2" t="n">
-        <v>4.410414395364829</v>
+        <v>4.402769168157422</v>
       </c>
       <c r="P2" t="n">
-        <v>382.8974091079835</v>
+        <v>382.9203065410877</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16596,28 +16670,28 @@
         <v>0.0755</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1793534392532174</v>
+        <v>0.1775826129074171</v>
       </c>
       <c r="J3" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K3" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1883222084062641</v>
+        <v>0.1864118810008988</v>
       </c>
       <c r="M3" t="n">
-        <v>2.247575436263133</v>
+        <v>2.245372787934772</v>
       </c>
       <c r="N3" t="n">
-        <v>8.306327397694588</v>
+        <v>8.286076350833321</v>
       </c>
       <c r="O3" t="n">
-        <v>2.882069984871046</v>
+        <v>2.878554559294182</v>
       </c>
       <c r="P3" t="n">
-        <v>379.186124937373</v>
+        <v>379.2046512184514</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16674,28 +16748,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1499010152594541</v>
+        <v>0.1484697968949104</v>
       </c>
       <c r="J4" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K4" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1264649196034459</v>
+        <v>0.1252643780583754</v>
       </c>
       <c r="M4" t="n">
-        <v>2.290297731233217</v>
+        <v>2.287561228908982</v>
       </c>
       <c r="N4" t="n">
-        <v>9.298800467943725</v>
+        <v>9.267071057388248</v>
       </c>
       <c r="O4" t="n">
-        <v>3.04939345902488</v>
+        <v>3.044186436043011</v>
       </c>
       <c r="P4" t="n">
-        <v>384.6812558336074</v>
+        <v>384.6962275685095</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16752,28 +16826,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1371894666024647</v>
+        <v>0.1376710717743413</v>
       </c>
       <c r="J5" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K5" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09765784959832735</v>
+        <v>0.09912336304986225</v>
       </c>
       <c r="M5" t="n">
-        <v>2.333235192665725</v>
+        <v>2.324787725210362</v>
       </c>
       <c r="N5" t="n">
-        <v>10.41869020713114</v>
+        <v>10.37030956479954</v>
       </c>
       <c r="O5" t="n">
-        <v>3.227799592157348</v>
+        <v>3.220296502622008</v>
       </c>
       <c r="P5" t="n">
-        <v>383.9322834973157</v>
+        <v>383.9272459362933</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16830,28 +16904,28 @@
         <v>0.1629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05461344938732469</v>
+        <v>0.05742917785086108</v>
       </c>
       <c r="J6" t="n">
+        <v>418</v>
+      </c>
+      <c r="K6" t="n">
         <v>416</v>
       </c>
-      <c r="K6" t="n">
-        <v>414</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02126107134359012</v>
+        <v>0.02354331332132276</v>
       </c>
       <c r="M6" t="n">
-        <v>2.187925194093971</v>
+        <v>2.190476086245657</v>
       </c>
       <c r="N6" t="n">
-        <v>8.099131922449347</v>
+        <v>8.108388543461034</v>
       </c>
       <c r="O6" t="n">
-        <v>2.845897384384994</v>
+        <v>2.847523229661355</v>
       </c>
       <c r="P6" t="n">
-        <v>384.9010189118291</v>
+        <v>384.8712151363484</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16889,7 +16963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G417"/>
+  <dimension ref="A1:G419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32273,6 +32347,80 @@
         </is>
       </c>
     </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>-36.78567982477016,175.09787124600913</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>-36.785622261166914,175.098718909839</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>-36.78538826620804,175.09954088598678</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-36.785128338305064,175.1003591144119</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-36.784847702104585,175.10118170597323</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>-36.78567646528924,175.097870422697</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>-36.78562365961117,175.0987193457951</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-36.78538647960835,175.09954011078943</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-36.785129588488424,175.1003597531292</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-36.784845795511025,175.10118069585465</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
